--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484532_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484532_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.339</v>
+        <v>3.5205</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7079</v>
+        <v>2.9142</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6311</v>
+        <v>0.6063</v>
       </c>
       <c r="G2" t="n">
         <v>0.2717</v>
@@ -610,13 +610,13 @@
         <v>1.8326</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.006</v>
+        <v>-0.8245</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.5645</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2352</v>
+        <v>-0.26</v>
       </c>
       <c r="V2" t="n">
         <v>3.157</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.956</v>
+        <v>2.6705</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6275</v>
+        <v>1.2429</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3285</v>
+        <v>1.4276</v>
       </c>
       <c r="G3" t="n">
         <v>1.4349</v>
@@ -688,13 +688,13 @@
         <v>1.2828</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3744</v>
+        <v>-0.6599</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0536</v>
+        <v>-0.3311</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4279</v>
+        <v>-0.3288</v>
       </c>
       <c r="V3" t="n">
         <v>0.6127</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8882</v>
+        <v>1.9651</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5251</v>
+        <v>0.6763</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3632</v>
+        <v>1.2889</v>
       </c>
       <c r="G4" t="n">
         <v>1.5894</v>
@@ -766,13 +766,13 @@
         <v>1.4661</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1672</v>
+        <v>-1.0903</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9728</v>
+        <v>-0.8216</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1944</v>
+        <v>-0.2687</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0866</v>
+        <v>1.3284</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4458</v>
+        <v>-0.2535</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5323</v>
+        <v>1.5819</v>
       </c>
       <c r="G5" t="n">
         <v>0.1295</v>
@@ -844,13 +844,13 @@
         <v>1.0995</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4436</v>
+        <v>-0.2017</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6976</v>
+        <v>-0.5053</v>
       </c>
       <c r="U5" t="n">
-        <v>0.254</v>
+        <v>0.3035</v>
       </c>
       <c r="V5" t="n">
         <v>0.3011</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6921</v>
+        <v>0.9727</v>
       </c>
       <c r="E6" t="n">
-        <v>0.851</v>
+        <v>1.0573</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1589</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>0.1268</v>
@@ -922,13 +922,13 @@
         <v>2.0158</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4897</v>
+        <v>-1.2091</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.2111</v>
+        <v>-1.0049</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2785</v>
+        <v>-0.2042</v>
       </c>
       <c r="V6" t="n">
         <v>0.9554</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0386</v>
+        <v>-0.4076</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5241</v>
+        <v>-0.3729</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4856</v>
+        <v>-0.0347</v>
       </c>
       <c r="G9" t="n">
         <v>1.6648</v>
@@ -1156,13 +1156,13 @@
         <v>0.9163</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1432</v>
+        <v>-0.5123</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5505</v>
+        <v>-0.3993</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4073</v>
+        <v>-0.113</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6439</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8248</v>
+        <v>-1.0335</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8228</v>
+        <v>-3.0562</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9979</v>
+        <v>2.0227</v>
       </c>
       <c r="G10" t="n">
         <v>-0.4665</v>
@@ -1234,13 +1234,13 @@
         <v>1.4661</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3138</v>
+        <v>-0.5224</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1666</v>
+        <v>-0.4001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1471</v>
+        <v>-0.1224</v>
       </c>
       <c r="V10" t="n">
         <v>0.3219</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8649</v>
+        <v>-1.6915</v>
       </c>
       <c r="E11" t="n">
         <v>1.5582</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.4231</v>
+        <v>-3.2497</v>
       </c>
       <c r="G11" t="n">
         <v>1.9124</v>
@@ -1312,13 +1312,13 @@
         <v>1.2828</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2592</v>
+        <v>-1.0858</v>
       </c>
       <c r="T11" t="n">
         <v>-0.9359</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3233</v>
+        <v>-0.1499</v>
       </c>
       <c r="V11" t="n">
         <v>-3.8009</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7533</v>
+        <v>-2.445</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6693</v>
+        <v>-2.5592</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.08400000000000001</v>
+        <v>0.1141</v>
       </c>
       <c r="G12" t="n">
         <v>-1.7099</v>
@@ -1390,13 +1390,13 @@
         <v>2.1991</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6823</v>
+        <v>-1.3741</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2662</v>
+        <v>-1.1561</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4162</v>
+        <v>-0.218</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6439</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.8117</v>
+        <v>-2.5861</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.7277</v>
+        <v>-2.5765</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0839</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-0.7171999999999999</v>
@@ -1468,13 +1468,13 @@
         <v>0.9163</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1782</v>
+        <v>-0.9527</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4774</v>
+        <v>-0.3262</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7008</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.552</v>
+        <v>-3.1639</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.7006</v>
+        <v>-3.5355</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1486</v>
+        <v>0.3716</v>
       </c>
       <c r="G14" t="n">
         <v>-2.9615</v>
@@ -1546,13 +1546,13 @@
         <v>1.4661</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8129</v>
+        <v>-1.4248</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.4864</v>
+        <v>-1.3212</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3265</v>
+        <v>-0.1035</v>
       </c>
       <c r="V14" t="n">
         <v>1.5889</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.3507</v>
+        <v>-4.5379</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.4152</v>
+        <v>-3.3051</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9355</v>
+        <v>-1.2328</v>
       </c>
       <c r="G15" t="n">
         <v>-3.1351</v>
@@ -1624,13 +1624,13 @@
         <v>1.4661</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1318</v>
+        <v>-1.319</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1561</v>
+        <v>-1.046</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0243</v>
+        <v>-0.273</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6335</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-5.258799999999999</v>
+        <v>-4.432999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-8.060499999999999</v>
+        <v>-7.2347</v>
       </c>
       <c r="F16" t="n">
-        <v>2.801800000000001</v>
+        <v>2.8017</v>
       </c>
       <c r="G16" t="n">
         <v>-0.8854000000000002</v>
@@ -1702,13 +1702,13 @@
         <v>17.4096</v>
       </c>
       <c r="S16" t="n">
-        <v>-12.0023</v>
+        <v>-11.1766</v>
       </c>
       <c r="T16" t="n">
-        <v>-9.637700000000002</v>
+        <v>-8.812200000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-2.3643</v>
+        <v>-2.3645</v>
       </c>
       <c r="V16" t="n">
         <v>1.2148</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>8.779400000000001</v>
+        <v>7.1112</v>
       </c>
       <c r="E17" t="n">
-        <v>6.761</v>
+        <v>5.4148</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0184</v>
+        <v>1.6964</v>
       </c>
       <c r="G17" t="n">
         <v>1.3637</v>
@@ -1780,13 +1780,13 @@
         <v>1.2828</v>
       </c>
       <c r="S17" t="n">
-        <v>4.4761</v>
+        <v>2.8079</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3236</v>
+        <v>0.9774</v>
       </c>
       <c r="U17" t="n">
-        <v>2.1525</v>
+        <v>1.8305</v>
       </c>
       <c r="V17" t="n">
         <v>3.4894</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. CAMPOS DE BENGOA</t>
+          <t>A. IGBINS DAVID</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.9718</v>
+        <v>2.6376</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2441</v>
+        <v>0.732</v>
       </c>
       <c r="F18" t="n">
-        <v>4.2159</v>
+        <v>1.9056</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1213</v>
+        <v>3.2441</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5767</v>
+        <v>3.0487</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4554</v>
+        <v>0.1953</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6292</v>
+        <v>3.4703</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5695</v>
+        <v>2.7618</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.1987</v>
+        <v>0.7085</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7504999999999999</v>
+        <v>-0.2262</v>
       </c>
       <c r="N18" t="n">
-        <v>1.0072</v>
+        <v>0.2869</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2567</v>
+        <v>-0.5131</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5498</v>
+        <v>-2.5656</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4661</v>
+        <v>1.0995</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2458</v>
+        <v>0.3807</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6026</v>
+        <v>-0.3401</v>
       </c>
       <c r="U18" t="n">
-        <v>2.6432</v>
+        <v>0.7208</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.945</v>
+        <v>1.5785</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3011</v>
+        <v>1.267</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6439</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. IGBINS DAVID</t>
+          <t>J. LE BERRE CASTILLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.3914</v>
+        <v>2.1953</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5397</v>
+        <v>1.5485</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8517</v>
+        <v>0.6468</v>
       </c>
       <c r="G19" t="n">
-        <v>3.2441</v>
+        <v>1.0916</v>
       </c>
       <c r="H19" t="n">
-        <v>3.0487</v>
+        <v>0.0977</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1953</v>
+        <v>0.9938</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4703</v>
+        <v>1.4979</v>
       </c>
       <c r="K19" t="n">
-        <v>2.7618</v>
+        <v>1.3373</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7085</v>
+        <v>0.1606</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2262</v>
+        <v>-0.4063</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2869</v>
+        <v>-1.2395</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5131</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.5656</v>
+        <v>0.9163</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.6651</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0995</v>
+        <v>0.9163</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1345</v>
+        <v>1.4336</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5324</v>
+        <v>0.0298</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6669</v>
+        <v>1.4038</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5785</v>
+        <v>-1.2461</v>
       </c>
       <c r="W19" t="n">
-        <v>1.267</v>
+        <v>0.0208</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3115</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. LE BERRE CASTILLO</t>
+          <t>A. CEJUDO GALÁN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.6591</v>
+        <v>1.6005</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2601</v>
+        <v>1.6005</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3991</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.0916</v>
+        <v>1.6005</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0977</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9938</v>
+        <v>0.6251</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4979</v>
+        <v>1.6005</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3373</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1606</v>
+        <v>0.6251</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4063</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2395</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8332000000000001</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8974</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2586</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1561</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2461</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.0208</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALÁN</t>
+          <t>J. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.6005</v>
+        <v>1.5322</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6005</v>
+        <v>-1.821</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>3.3532</v>
       </c>
       <c r="G21" t="n">
-        <v>1.6005</v>
+        <v>0.1213</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9752999999999999</v>
+        <v>1.5767</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6251</v>
+        <v>-1.4554</v>
       </c>
       <c r="J21" t="n">
-        <v>1.6005</v>
+        <v>-0.6292</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.5695</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6251</v>
+        <v>-1.1987</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>0.7504999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.0072</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-0.2567</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.4661</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.8062</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>0.0257</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.7805</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.945</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.3011</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="22">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1774</v>
+        <v>0.4688</v>
       </c>
       <c r="E23" t="n">
-        <v>2.6338</v>
+        <v>2.8261</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4564</v>
+        <v>-2.3573</v>
       </c>
       <c r="G23" t="n">
         <v>1.1226</v>
@@ -2248,13 +2248,13 @@
         <v>0.5498</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6882</v>
+        <v>0.9796</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2919</v>
+        <v>0.4842</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3964</v>
+        <v>0.4955</v>
       </c>
       <c r="V23" t="n">
         <v>-1.267</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G. VOLPATO</t>
+          <t>J. VILLAR SOLER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.4115</v>
+        <v>-1.2706</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0388</v>
+        <v>-2.6417</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3727</v>
+        <v>1.3711</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.5764</v>
+        <v>-2.512</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2495</v>
+        <v>-0.1305</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.3269</v>
+        <v>-2.3815</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5245</v>
+        <v>-2.1316</v>
       </c>
       <c r="K24" t="n">
-        <v>0.065</v>
+        <v>0.2818</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5895</v>
+        <v>-2.4133</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.0519</v>
+        <v>-0.3804</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3145</v>
+        <v>-0.4122</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7374000000000001</v>
+        <v>0.0318</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.3665</v>
+        <v>0.1833</v>
       </c>
       <c r="Q24" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5498</v>
+        <v>1.0995</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7983</v>
+        <v>1.0581</v>
       </c>
       <c r="T24" t="n">
-        <v>0.402</v>
+        <v>0.4061</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3964</v>
+        <v>0.6519</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. VILLAR SOLER</t>
+          <t>J. SABATE PRATS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.611</v>
+        <v>-1.6434</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.5071</v>
+        <v>-5.7861</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8961</v>
+        <v>4.1427</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.512</v>
+        <v>-2.2442</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1305</v>
+        <v>0.1503</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.3815</v>
+        <v>-2.3945</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.1316</v>
+        <v>-3.5076</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2818</v>
+        <v>-0.9852</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.4133</v>
+        <v>-2.5224</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.3804</v>
+        <v>1.2634</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.4122</v>
+        <v>1.1354</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0318</v>
+        <v>0.1279</v>
       </c>
       <c r="P25" t="n">
-        <v>0.1833</v>
+        <v>-2.0158</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R25" t="n">
-        <v>1.0995</v>
+        <v>1.6493</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2824</v>
+        <v>1.0173</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4593</v>
+        <v>-0.2126</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1769</v>
+        <v>1.23</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.5993</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.5993</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>D. GARCIA ROYO</t>
+          <t>P. MORTE MONTANES</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.6346</v>
+        <v>-2.3256</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.4657</v>
+        <v>-3.736</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.169</v>
+        <v>1.4104</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.7168</v>
+        <v>-1.5591</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.4444</v>
+        <v>-0.5621</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7276</v>
+        <v>-0.997</v>
       </c>
       <c r="J26" t="n">
-        <v>1.002</v>
+        <v>-0.3528</v>
       </c>
       <c r="K26" t="n">
-        <v>0.2102</v>
+        <v>-0.446</v>
       </c>
       <c r="L26" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.7189</v>
+        <v>-1.2063</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.6546</v>
+        <v>-0.1161</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.0643</v>
+        <v>-1.0902</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.2828</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.8326</v>
+        <v>-2.7489</v>
       </c>
       <c r="R26" t="n">
-        <v>0.5498</v>
+        <v>1.8326</v>
       </c>
       <c r="S26" t="n">
-        <v>1.577</v>
+        <v>1.0948</v>
       </c>
       <c r="T26" t="n">
-        <v>0.9879</v>
+        <v>-0.0113</v>
       </c>
       <c r="U26" t="n">
-        <v>0.5891</v>
+        <v>1.1061</v>
       </c>
       <c r="V26" t="n">
-        <v>-2.212</v>
+        <v>-0.945</v>
       </c>
       <c r="W26" t="n">
         <v>-0.6231</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.5889</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>P. MORTE MONTANES</t>
+          <t>G. VOLPATO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,73 +2515,73 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.77</v>
+        <v>-2.6009</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.9283</v>
+        <v>-1.3273</v>
       </c>
       <c r="F27" t="n">
-        <v>1.1583</v>
+        <v>-1.2736</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.5591</v>
+        <v>-1.5764</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.5621</v>
+        <v>-0.2495</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.997</v>
+        <v>-1.3269</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.3528</v>
+        <v>-0.5245</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.446</v>
+        <v>0.065</v>
       </c>
       <c r="L27" t="n">
-        <v>0.09320000000000001</v>
+        <v>-0.5895</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.2063</v>
+        <v>-1.0519</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.1161</v>
+        <v>-0.3145</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.0902</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="P27" t="n">
+        <v>-0.3665</v>
+      </c>
+      <c r="Q27" t="n">
         <v>-0.9163</v>
       </c>
-      <c r="Q27" t="n">
-        <v>-2.7489</v>
-      </c>
       <c r="R27" t="n">
-        <v>1.8326</v>
+        <v>0.5498</v>
       </c>
       <c r="S27" t="n">
-        <v>0.6505</v>
+        <v>0.609</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.2036</v>
+        <v>0.1135</v>
       </c>
       <c r="U27" t="n">
-        <v>0.854</v>
+        <v>0.4955</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.945</v>
+        <v>-1.267</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.3219</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>J. SABATE PRATS</t>
+          <t>D. GARCIA ROYO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2593,67 +2593,67 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.844</v>
+        <v>-2.7556</v>
       </c>
       <c r="E28" t="n">
-        <v>-6.363</v>
+        <v>-0.5618</v>
       </c>
       <c r="F28" t="n">
-        <v>3.519</v>
+        <v>-2.1937</v>
       </c>
       <c r="G28" t="n">
-        <v>-2.2442</v>
+        <v>-0.7168</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1503</v>
+        <v>-1.4444</v>
       </c>
       <c r="I28" t="n">
-        <v>-2.3945</v>
+        <v>0.7276</v>
       </c>
       <c r="J28" t="n">
-        <v>-3.5076</v>
+        <v>1.002</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.9852</v>
+        <v>0.2102</v>
       </c>
       <c r="L28" t="n">
-        <v>-2.5224</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>1.2634</v>
+        <v>-1.7189</v>
       </c>
       <c r="N28" t="n">
-        <v>1.1354</v>
+        <v>-1.6546</v>
       </c>
       <c r="O28" t="n">
-        <v>0.1279</v>
+        <v>-0.0643</v>
       </c>
       <c r="P28" t="n">
-        <v>-2.0158</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q28" t="n">
-        <v>-3.6651</v>
+        <v>-1.8326</v>
       </c>
       <c r="R28" t="n">
-        <v>1.6493</v>
+        <v>0.5498</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.1833</v>
+        <v>1.4561</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.7896</v>
+        <v>0.8918</v>
       </c>
       <c r="U28" t="n">
-        <v>0.6063</v>
+        <v>0.5643</v>
       </c>
       <c r="V28" t="n">
-        <v>1.5993</v>
+        <v>-2.212</v>
       </c>
       <c r="W28" t="n">
-        <v>1.5993</v>
+        <v>-0.6231</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="29">
@@ -2671,31 +2671,31 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>5.258700000000003</v>
+        <v>5.899700000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.801700000000001</v>
+        <v>-2.801800000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>8.060400000000001</v>
+        <v>8.701600000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>0.8854999999999995</v>
+        <v>0.8855000000000001</v>
       </c>
       <c r="H29" t="n">
         <v>3.4493</v>
       </c>
       <c r="I29" t="n">
-        <v>-2.564099999999999</v>
+        <v>-2.5641</v>
       </c>
       <c r="J29" t="n">
-        <v>7.414</v>
+        <v>7.413999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>7.571600000000001</v>
+        <v>7.571600000000002</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.1576000000000004</v>
+        <v>-0.1576000000000001</v>
       </c>
       <c r="M29" t="n">
         <v>-6.528599999999999</v>
@@ -2716,13 +2716,13 @@
         <v>10.9955</v>
       </c>
       <c r="S29" t="n">
-        <v>12.0021</v>
+        <v>12.6433</v>
       </c>
       <c r="T29" t="n">
         <v>2.3645</v>
       </c>
       <c r="U29" t="n">
-        <v>9.637799999999999</v>
+        <v>10.2789</v>
       </c>
       <c r="V29" t="n">
         <v>-1.2149</v>
@@ -2731,7 +2731,7 @@
         <v>4.8292</v>
       </c>
       <c r="X29" t="n">
-        <v>-6.0442</v>
+        <v>-6.044199999999999</v>
       </c>
     </row>
   </sheetData>
